--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0018.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0018.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Xem Sonata Effect</t>
+          <t>Đi kiểm tra Hiệu Ứng Sonata</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn có thể lọc &lt;color=#8c7e51&gt;COST&lt;/color&gt; và bộ &lt;color=#8c7e51&gt;Sonata Effect&lt;/color&gt; của Echo</t>
+          <t>Cậu có thể lọc &lt;color=#8c7e51&gt;CHI PHÍ&lt;/color&gt; và bộ &lt;color=#8c7e51&gt;Hiệu Ứng Sonata&lt;/color&gt; của Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Equip Echoes cùng Sonata để kích hoạt Sonata Effect.</t>
+          <t>Gắn Echo cùng Bản Giao Hưởng để kích hoạt Hiệu Ứng Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bạn có thể tìm vị trí kẻ địch trong &lt;color=#8c7e51&gt;Cẩm Nang&lt;/color&gt;</t>
+          <t>Bạn có thể tìm vị trí địch trong &lt;color=#8c7e51&gt;Sổ tay Hướng dẫn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bạn có thể tìm vị trí kẻ địch trong &lt;color=#8c7e51&gt;Cẩm nang&lt;/color&gt;</t>
+          <t>Bạn có thể tìm vị trí địch trong &lt;color=#8c7e51&gt;Sổ tay Hướng dẫn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Rover có thể tiêu hao Forte Gauge để sử dụng &lt;color=#8c7e51&gt;Resonance Skill được tăng cường&lt;/color&gt;</t>
+          <t>Rover có thể tiêu hao Đồng Vọng để thi triển &lt;color=#8c7e51&gt;Resonance Skill được tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Rover có thể tiêu hao Forte Gauge để sử dụng &lt;color=#8c7e51&gt;Resonance Skill được tăng cường&lt;/color&gt;</t>
+          <t>Rover có thể tiêu hao Đồng Vọng để thi triển &lt;color=#8c7e51&gt;Resonance Skill được tăng cường&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Khi Vibration Strength giảm về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Bất Động&lt;/color&gt; và không thể thực hiện hành động trong một khoảng thời gian.</t>
+          <t>Khi Sức Rung giảm về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Bất Động&lt;/color&gt; và không thể thực hiện bất kỳ hành động nào trong một khoảng thời gian.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Khi Vibration Strength giảm về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Bất Động&lt;/color&gt; và không thể thực hiện hành động trong một khoảng thời gian.</t>
+          <t>Khi Sức Rung giảm về 0, kẻ địch sẽ bị &lt;color=#8c7e51&gt;Bất Động&lt;/color&gt; và không thể thực hiện bất kỳ hành động nào trong một khoảng thời gian.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>{0} Sử dụng chức năng Kéo để di chuyển các vật thể lớn.</t>
+          <t>Dùng chức năng Pull để di chuyển các vật thể lớn.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dùng chức năng Kéo để di chuyển vật thể lớn.</t>
+          <t>Dùng chức năng Kéo để di chuyển các vật thể lớn.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Set giờ</t>
+          <t>Đặt thời gian theo chỉ định</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>{0} Dùng &lt;color=#8c7e51&gt;Resonance Skill&lt;/color&gt; này để lao về phía trước</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Kỹ Năng Vọng Âm&lt;/color&gt; này để lao về phía trước</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>{0} Khi Forte Gauge trên 50%, dùng Resonance Skill sẽ tự động tiêu hao để tung ra Resonance Skill được tăng cường.</t>
+          <t>Khi Thanh Forte trên 50%, sử dụng Resonance Skill sẽ tự động tiêu hao để thi triển phiên bản Resonance Skill được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Thực hiện tấn công để nhận &lt;color=#8c7e51&gt;Forte Gauge&lt;/color&gt;.</t>
+          <t>Tấn công để tích lũy &lt;color=#8c7e51&gt;Đồng Vọng Cường Độ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Khi Forte Gauge trên 50%, dùng Resonance Skill sẽ tự động tiêu hao để tung ra Resonance Skill được tăng cường.</t>
+          <t>Khi Thanh Forte trên 50%, hãy dùng Resonance Skill để tự động tiêu hao và tung ra Resonance Skill được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>An error occurred Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Đã xảy ra lỗi. Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kẻ địch còn Vibration Strength sẽ khó đánh bại hơn. &lt;color=#8c7e51&gt;Phản đòn&lt;/color&gt; có thể giảm đáng kể Vibration Strength của chúng.</t>
+          <t>Kẻ địch còn Lực Rung Động sẽ khó bị đánh bại hơn. &lt;color=#8c7e51&gt;Phản Đòn&lt;/color&gt; có thể làm giảm đáng kể Lực Rung Động của chúng.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Gây sát thương để giảm Sức mạnh Vibration của kẻ địch. &lt;color=#8c7e51&gt;Phản công&lt;/color&gt; làm giảm đáng kể Sức mạnh Vibration.</t>
+          <t>Gây sát thương để giảm Sức Mạnh Dao Động của kẻ địch. &lt;color=#8c7e51&gt;Phản Đòn&lt;/color&gt; sẽ làm giảm đáng kể Sức Mạnh Dao Động.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi phong cách hình ảnh của game tại đây.</t>
+          <t>Cậu có thể thay đổi phong cách hình ảnh của trò chơi tại đây.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi phong cách hình ảnh của game tại đây.</t>
+          <t>Cậu có thể thay đổi phong cách hình ảnh của trò chơi tại đây.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Bạn có thể thay đổi phong cách hình ảnh của game tại đây.</t>
+          <t>Cậu có thể thay đổi phong cách hình ảnh của trò chơi tại đây.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một bộ lọc kiểu hình ảnh định sẵn tại đây.</t>
+          <t>Cậu có thể chọn bộ lọc phong cách hình ảnh có sẵn tại đây.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một bộ lọc kiểu hình ảnh định sẵn tại đây.</t>
+          <t>Cậu có thể chọn bộ lọc phong cách hình ảnh có sẵn tại đây.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một bộ lọc kiểu hình ảnh định sẵn tại đây.</t>
+          <t>Cậu có thể chọn bộ lọc phong cách hình ảnh có sẵn tại đây.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Sau khi chọn bộ lọc cài sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
+          <t>Sau khi chọn bộ lọc có sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sau khi chọn bộ lọc cài sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
+          <t>Sau khi chọn bộ lọc có sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Sau khi chọn bộ lọc cài sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
+          <t>Sau khi chọn bộ lọc có sẵn, bạn có thể tinh chỉnh hiệu ứng hình ảnh tại đây.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} Apply để sử dụng bộ lọc.</t>
+          <t>Nhấn để sử dụng bộ lọc.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} Apply để sử dụng bộ lọc.</t>
+          <t>Nhấn để sử dụng bộ lọc.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} Apply để sử dụng bộ lọc.</t>
+          <t>Nhấn để sử dụng bộ lọc.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Invite tối đa 3 Đồng hành đến đây thư giãn cùng bạn.</t>
+          <t>Mời tối đa 3 Cộng Hưởng Giả đồng hành cùng bạn thư giãn tại đây.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Invite tối đa 3 Đồng hành đến đây thư giãn cùng bạn.</t>
+          <t>Mời tối đa 3 Cộng Hưởng Giả đồng hành cùng bạn thư giãn tại đây.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Invite tối đa 3 Đồng hành đến đây thư giãn cùng bạn.</t>
+          <t>Mời tối đa 3 Cộng Hưởng Giả đồng hành cùng bạn thư giãn tại đây.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Dùng nút này để đặt vị trí cho Companions.</t>
+          <t>Dùng nút này để đặt vị trí cho Đồng Hành của bạn.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Dùng nút này để đặt vị trí cho Companions.</t>
+          <t>Dùng nút này để đặt vị trí cho Đồng Hành của bạn.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Dùng nút này để đặt vị trí cho Companions.</t>
+          <t>Dùng nút này để đặt vị trí cho Đồng Hành của bạn.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào chế độ góc nhìn thứ nhất.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang góc nhìn thứ nhất.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào chế độ góc nhìn thứ nhất.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang góc nhìn thứ nhất.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để vào chế độ góc nhìn thứ nhất.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chuyển sang góc nhìn thứ nhất.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Dùng nút này để thay đổi hướng của Trọng lực.</t>
+          <t>Dùng nút này để thay đổi hướng của Trọng Lực.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Nút này thay đổi hướng của Trọng lực.</t>
+          <t>Nút này thay đổi hướng của Trọng Lực.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Nút này thay đổi hướng của Trọng lực.</t>
+          <t>Nút này thay đổi hướng của Trọng Lực.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{0} Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;, bạn có thể có được đồng đội đáng tin cậy và vũ khí tiện dụng</t>
+          <t>{0} Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;, cậu có thể có được những đồng đội đáng tin cậy và vũ khí tiện dụng.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;. Bạn có thể tìm được những người đồng hành đáng tin cậy và vũ khí tiện dụng tại đây.</t>
+          <t>Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;, cậu có thể tìm được những người đồng hành đáng tin cậy và vũ khí hữu dụng ở đây.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>{0} Mở Resonators menus</t>
+          <t>Mở danh sách Resonator.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Khi ??? bị **Bất Động**, tiếp cận để dùng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt;</t>
+          <t>Khi ??? bị Hóa Đá, hãy tiếp cận để sử dụng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Khi ??? bị **Bất Động**, tiếp cận để dùng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt;</t>
+          <t>Khi ??? bị Hóa Đá, hãy tiếp cận để sử dụng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Những tạo vật trong mơ này được gọi là Illusive Echoes.</t>
+          <t>Những sinh vật mộng mị này được gọi là Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Những tạo vật trong mơ này được gọi là Illusive Echoes.</t>
+          <t>Những sinh vật mộng mị này được gọi là Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Những tạo vật trong mơ này được gọi là Illusive Echoes.</t>
+          <t>Những sinh vật mộng mị này được gọi là Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng yêu cầu của "Ẩn Dụ" loại cụ thể để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng "Ẩn Dụ" loại cụ thể để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng yêu cầu của "Ẩn Dụ" loại cụ thể để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng "Ẩn Dụ" loại cụ thể để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Thu thập đủ số lượng yêu cầu của "Ẩn Dụ" loại cụ thể để mở khóa thêm khả năng của Illusive Echo.</t>
+          <t>Thu thập đủ số lượng "Ẩn Dụ" loại cụ thể để mở khóa thêm kỹ năng của Illusive Echo</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>"Metaphor" cung cấp buff đặc biệt.</t>
+          <t>"Ẩn Dụ" cung cấp những hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>"Metaphor" cung cấp buff đặc biệt.</t>
+          <t>"Ẩn Dụ" cung cấp những hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>"Metaphor" cung cấp buff đặc biệt.</t>
+          <t>"Ẩn Dụ" cung cấp những hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Explore Somnoire để kiếm "Dream Fragments", có thể dùng để mua Metaphor và các vật phẩm khác trong một số Vùng Ký Ức</t>
+          <t>Khám phá Somnoire để thu thập "Mảnh Giấc Mơ", có thể dùng để mua Ẩn Dụ và các vật phẩm khác trong một số Vùng Ký Ức</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Explore Somnoire để kiếm "Dream Fragments", có thể dùng để mua Metaphor và các vật phẩm khác trong một số Vùng Ký Ức</t>
+          <t>Khám phá Somnoire để thu thập "Mảnh Giấc Mơ", có thể dùng để mua Ẩn Dụ và các vật phẩm khác trong một số Vùng Ký Ức</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Explore Somnoire để kiếm "Dream Fragments", có thể dùng để mua Metaphor và các vật phẩm khác trong một số Vùng Ký Ức</t>
+          <t>Khám phá Somnoire để thu thập "Mảnh Giấc Mơ", có thể dùng để mua Ẩn Dụ và các vật phẩm khác trong một số Vùng Ký Ức</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn Dụ" thuộc loại nhất định</t>
+          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn dụ" nhất định.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn Dụ" thuộc loại nhất định</t>
+          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn dụ" nhất định.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn Dụ" thuộc loại nhất định</t>
+          <t>Có thể mở khóa thêm khả năng khi đạt đủ số lượng "Ẩn dụ" nhất định.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>{0} Khi Năng Lượng đầy, bạn có thể biến hình thành Crownless.</t>
+          <t>Khi Năng Lượng đầy đủ, bạn có thể biến hình thành Crownless.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng của bạn đầy, nhấn {0}+{1} để biến hình thành Crownless.</t>
+          <t>Khi Năng Lượng của cậu đầy, nhấn {0}+{1} để biến hình thành Crownless.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Khi Năng Lượng của bạn đầy, bạn có thể biến hình thành Crownless.</t>
+          <t>Khi Năng Lượng của cậu đầy, cậu có thể biến hình thành Crownless.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Khi nhận được [Concerto Metaphor], bạn có thể mở khóa Đồng Hành Hỗ Trợ.</t>
+          <t>Khi nhận được [Concerto Metaphor], cậu có thể mở khóa một Đồng Hành Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Khi nhận được [Concerto Metaphor], bạn có thể mở khóa Đồng Hành Hỗ Trợ.</t>
+          <t>Khi nhận được [Concerto Metaphor], cậu có thể mở khóa một Đồng Hành Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Khi nhận được [Concerto Metaphor], bạn có thể mở khóa Đồng Hành Hỗ Trợ.</t>
+          <t>Khi nhận được [Concerto Metaphor], cậu có thể mở khóa một Đồng Hành Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Trong khi thu thập "Ẩn Dụ", bạn cũng sẽ nhận được thêm buff chỉ số.</t>
+          <t>Trong lúc thu thập "Phép Ẩn Dụ", bạn cũng sẽ nhận được thêm các hiệu ứng tăng thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{0} Khi thu thập "Ẩn Dụ", bạn cũng sẽ nhận thêm hiệu ứng tăng chỉ số.</t>
+          <t>Trong lúc thu thập "Ẩn Dụ", bạn cũng sẽ nhận được thêm hiệu ứng tăng thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Trong khi thu thập "Ẩn Dụ", bạn cũng sẽ nhận được thêm buff chỉ số.</t>
+          <t>Trong lúc thu thập "Phép Ẩn Dụ", bạn cũng sẽ nhận được thêm các hiệu ứng tăng thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Đồng Hành Hỗ Trợ</t>
+          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Cộng Sự Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Đồng Hành Hỗ Trợ</t>
+          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Cộng Sự Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Đồng Hành Hỗ Trợ</t>
+          <t>Khi Concerto Energy đầy, bạn có thể triệu hồi Cộng Sự Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Đồng Hành Hỗ Trợ sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Hỗ Trợ sẽ tung chiêu Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Đồng Hành Hỗ Trợ sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Hỗ Trợ sẽ tung chiêu Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Đồng Hành Hỗ Trợ sẽ thi triển Resonance Liberation khi được triệu hồi.</t>
+          <t>Đồng Hành Hỗ Trợ sẽ tung chiêu Resonance Liberation khi được triệu hồi.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Chọn "Tăng cường Nhân vật" để trao cho Nhân vật khả năng đặc biệt không có ngoài Illusive Realm.</t>
+          <t>Chọn "Character Enhancement" để trao cho Nhân Vật một khả năng đặc biệt không có ngoài Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Chọn "Tăng cường Nhân vật" để trao cho Nhân vật khả năng đặc biệt không có ngoài Illusive Realm.</t>
+          <t>Chọn "Character Enhancement" để trao cho Nhân Vật một khả năng đặc biệt không có ngoài Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Chọn "Tăng cường Nhân vật" để trao cho Nhân vật khả năng đặc biệt không có ngoài Illusive Realm.</t>
+          <t>Chọn "Character Enhancement" để trao cho Nhân Vật một khả năng đặc biệt không có ngoài Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Kiểm tra "Metaphors" và các nâng cấp bạn đã nhận được.</t>
+          <t>Kiểm tra các "Ẩn Dụ" và nâng cấp mà cậu đã nhận được.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Nhấn {0}+{1} để xem "Ẩn Dụ" sở hữu và các nâng cấp hiện tại bạn đã nhận được.</t>
+          <t>Nhấn {0}+{1} để xem "Ẩn Dụ" sở hữu và các nâng cấp hiện tại của cậu.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Kiểm tra "Metaphors" và các nâng cấp bạn đã nhận được.</t>
+          <t>Kiểm tra các "Ẩn Dụ" và nâng cấp mà cậu đã nhận được.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Mua buff trong "Tiến Hóa Tư Tưởng" bằng "Memory Points" thu được từ điều tra.</t>
+          <t>Mua các hiệu ứng tăng cường trong "Tiến Hóa Ý Niệm" bằng "Điểm Ký Ức" kiếm được từ điều tra.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Mua buff trong "Tiến Hóa Tư Tưởng" bằng "Memory Points" thu được từ điều tra.</t>
+          <t>Mua các hiệu ứng tăng cường trong "Tiến Hóa Ý Niệm" bằng "Điểm Ký Ức" kiếm được từ điều tra.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Mua buff trong "Tiến Hóa Tư Tưởng" bằng "Memory Points" thu được từ điều tra.</t>
+          <t>Mua các hiệu ứng tăng cường trong "Tiến Hóa Ý Niệm" bằng "Điểm Ký Ức" kiếm được từ điều tra.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong "Illusive Realm".</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong "Illusive Realm".</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong "Illusive Realm".</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong "Illusive Realm".</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Buffs sẽ tăng cường khả năng của Resonators trong "Illusive Realm".</t>
+          <t>Buff sẽ tăng cường khả năng của Resonator trong "Illusive Realm".</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Gây sát thương để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>Gây sát thương để tích &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Gây sát thương để nhận &lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt;.</t>
+          <t>Gây sát thương để tích &lt;color=#8c7e51&gt;Năng Lượng Giao Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt; đã đầy. Switch nhân vật ngay để kích hoạt &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt; của &lt;color=#8c7e51&gt;Chixia&lt;/color&gt;.</t>
+          <t>Năng lượng &lt;color=#8c7e51&gt;Concerto&lt;/color&gt; đã đầy. Chuyển sang nhân vật ngay để kích hoạt &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt; của &lt;color=#8c7e51&gt;Chixia&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Concerto Energy&lt;/color&gt; đã đầy. Switch nhân vật ngay để kích hoạt &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt; của &lt;color=#8c7e51&gt;Chixia&lt;/color&gt;.</t>
+          <t>Năng lượng &lt;color=#8c7e51&gt;Concerto&lt;/color&gt; đã đầy. Chuyển sang nhân vật ngay để kích hoạt &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt; của &lt;color=#8c7e51&gt;Chixia&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Yangyang và để &lt;color=#8c7e51&gt;Chixia rời đội và sử dụng Leaping Flames&lt;/color&gt;.</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Yangyang và để &lt;color=#8c7e51&gt;Chixia rời trận, kích hoạt Lửa Nhảy Múa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Yangyang và để &lt;color=#8c7e51&gt;Chixia thoát ra và sử dụng Bước Nhảy Lửa&lt;/color&gt;.</t>
+          <t>Chuyển sang &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; và để &lt;color=#8c7e51&gt;Chixia&lt;/color&gt; rời đi và thi triển &lt;color=#8c7e51&gt;Leaping Flames&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{0} &lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Chixia và để &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; rời đi và sử dụng &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt;.</t>
+          <t>{0} &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt; sang Chixia và để &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; rời trận, kích hoạt &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Switch&lt;/color&gt; sang Chixia và để &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; rời đi và dùng &lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt;.</t>
+          <t>Chuyển sang &lt;color=#8c7e51&gt;Chixia&lt;/color&gt; và để &lt;color=#8c7e51&gt;Yangyang&lt;/color&gt; rời đi và tung &lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Outro Skill&lt;/color&gt; của Yangyang phục hồi thêm &lt;color=#8c7e51&gt;Resonance Energy&lt;/color&gt; cho Character tiếp theo.</t>
+          <t>&lt;color=#8c7e51&gt;Kỹ Năng Outro&lt;/color&gt; của Yangyang phục hồi thêm &lt;color=#8c7e51&gt;Resonance Energy&lt;/color&gt; cho Nhân Vật tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Sau khi Dodge thành công, nhấn để kích hoạt &lt;color=#ffd12f&gt;Dodge Counter&lt;/color&gt;.</t>
+          <t>Sau khi né thành công, nhấn để kích hoạt &lt;color=#ffd12f&gt;Dodge Counter Tránh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Sau khi Dodge phản công thành công, nhấn để kích hoạt &lt;color=#ffd12f&gt;Đòn Liên Kết Special&lt;/color&gt;.</t>
+          <t>Sau khi né phản công thành công, nhấn để kích hoạt &lt;color=#ffd12f&gt;Đòn Liên Kết Đặc Biệt&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Đòn tấn công đặc biệt được tăng cường của Yangyang là &lt;color=#8c7e51&gt;Heavy Attack: Zephyr Song&lt;/color&gt;. Nó sẽ tạo ra &lt;color=#8c7e51&gt;"Melody"&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Đòn Tấn Công Đặc Biệt Nâng Cao của Yangyang là &lt;color=#8c7e51&gt;Heavy Attack: Zephyr Song&lt;/color&gt;. Nó sẽ tạo ra &lt;color=#8c7e51&gt;"Melody"&lt;/color&gt; khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>{0} Resonance Conversion unlocked.</t>
+          <t>Chuyển Đổi Cộng Hưởng đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Đã mở khóa Resonance Conversion.</t>
+          <t>Chuyển Hóa Cộng Hưởng đã được mở khóa.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>{0} Resonance Conversion unlocked.</t>
+          <t>Chuyển Đổi Cộng Hưởng đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Resonance Conversion đã mở khóa</t>
+          <t>Đã Mở Khóa Chuyển Hóa Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Attribute Resonance của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Havoc.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã nhận. Nhấn {0} để xem Echo trong bảng Resonators.</t>
+          <t>&lt;color=#8c7e51&gt;Echo&lt;/color&gt; đã thu thập. Nhấn {0} để xem &lt;color=#8c7e51&gt;Echo&lt;/color&gt; trong bảng Resonator.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Enter bảng Resonators để trang bị Echoes</t>
+          <t>Vào bảng Resonator để trang bị Echo.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Equip Echo để mở khóa kỹ năng mới</t>
+          <t>Trang bị Echo để mở khóa kỹ năng mới</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mở để xem bảng Equip Echoes</t>
+          <t>Mở bảng Trang Bị Echo</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>{0} Equip the Echo để mở khóa Echo Skill và tăng chỉ số</t>
+          <t>{0} Trang bị Echo để mở khóa Kỹ Năng Echo và Tăng Chỉ Số</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Resonators có thể sử dụng &lt;color=#8c7e51&gt;Resonance Skill&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên</t>
+          <t>Resonator có thể sử dụng &lt;color=#8c7e51&gt;Kỹ Năng Echo&lt;/color&gt; của Echo được trang bị ở vị trí đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Đồng Hồ Forte: Concentration</t>
+          <t>Tần số: Tập trung</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Đồng Hồ Forte: Concentration</t>
+          <t>Tần số: Tập trung</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Khi Basic Attack trúng mục tiêu, nhận 1 "Concentration".</t>
+          <t>Khi Đòn Basic Attack trúng mục tiêu, nhận 1 "Concentration".</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Khi Basic Attack trúng mục tiêu, nhận 1 "Concentration".</t>
+          <t>Khi Đòn Basic Attack trúng mục tiêu, nhận 1 "Concentration".</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Photosynthesis Energy" khi đánh trúng mục tiêu bằng Basic Attack V.</t>
+          <t>Nhận 1 tầng "Năng Lượng Quang Hợp" khi trúng đòn Đòn Basic Attack V vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Photosynthesis Energy" khi đánh trúng mục tiêu bằng Basic Attack V.</t>
+          <t>Nhận 1 tầng "Năng Lượng Quang Hợp" khi trúng đòn Đòn Basic Attack V vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Gây 1 tầng "Photosynthesis Energy" khi trúng mục tiêu bằng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Năng Lượng Quang Hợp" khi trúng đòn Resonance Skill vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Gây 1 tầng "Photosynthesis Energy" khi trúng mục tiêu bằng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Năng Lượng Quang Hợp" khi trúng đòn Resonance Skill vào mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Khi tấn công trúng mục tiêu, phục hồi [Mayhem]</t>
+          <t>Khi tấn công trúng mục tiêu, hồi phục [Mayhem].</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Khi tấn công trúng mục tiêu, phục hồi [Mayhem]</t>
+          <t>Khi tấn công trúng mục tiêu, hồi phục [Mayhem].</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nhận "Âm Thanh Nhỏ" khi Normal Attack trúng mục tiêu.</t>
+          <t>Nhận "Âm Thanh Nhỏ" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nhận "Âm Thanh Nhỏ" khi Normal Attack trúng mục tiêu.</t>
+          <t>Nhận "Âm Thanh Nhỏ" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Nhận "Âm Thanh Nhỏ Bé" khi sử dụng Intro Skill.</t>
+          <t>Nhận "Âm Thanh Nhỏ" khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Nhận "Âm Thanh Nhỏ Bé" khi sử dụng Intro Skill.</t>
+          <t>Nhận "Âm Thanh Nhỏ" khi sử dụng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Nhận lượng lớn "Âm Thanh Nhỏ" khi đánh trúng mục tiêu bằng combo đúng nhịp.</t>
+          <t>Tấn công mục tiêu bằng chuỗi đòn chuẩn xác sẽ nhận được lượng lớn "Âm Thanh Nhỏ Bé".</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nhận lượng lớn "Âm Thanh Nhỏ" khi đánh trúng mục tiêu bằng combo đúng nhịp.</t>
+          <t>Tấn công mục tiêu bằng chuỗi đòn chuẩn xác sẽ nhận được lượng lớn "Âm Thanh Nhỏ Bé".</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Mỗi tầng "Thanh Minh" sẽ mở rộng phạm vi "Băng Giá". Giữ tối đa 2 tầng "Thanh Minh".</t>
+          <t>Mỗi lớp "Clarity" sẽ mở rộng phạm vi "Frostbite". Có thể giữ tối đa 2 lớp "Clarity".</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mỗi tầng "Thanh Minh" sẽ mở rộng phạm vi "Băng Giá". Giữ tối đa 2 tầng "Thanh Minh".</t>
+          <t>Mỗi lớp "Clarity" sẽ mở rộng phạm vi "Frostbite". Có thể giữ tối đa 2 lớp "Clarity".</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Clarity" khi sử dụng Basic Attack V.</t>
+          <t>Nhận 1 tầng "Sáng Suốt" khi sử dụng Đòn Basic Attack V.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Clarity" khi sử dụng Basic Attack V.</t>
+          <t>Nhận 1 tầng "Sáng Suốt" khi sử dụng Đòn Basic Attack V.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Clarity" khi sử dụng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Sáng Suốt" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Nhận 1 tầng "Clarity" khi sử dụng Resonance Skill.</t>
+          <t>Nhận 1 tầng "Sáng Suốt" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Nhận 2 tầng "Clarity" khi sử dụng Resonance Liberation.</t>
+          <t>Nhận 2 tầng "Thanh Tịnh" khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Nhận 2 tầng "Clarity" khi sử dụng Resonance Liberation.</t>
+          <t>Nhận 2 tầng "Thanh Tịnh" khi kích hoạt Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Nhận "Thermobaric Bullets" khi Đòn Tấn Công Thường trúng mục tiêu.</t>
+          <t>Nhận "Đạn Nhiệt Áp" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Nhận "Thermobaric Bullets" khi Đòn Tấn Công Thường trúng mục tiêu.</t>
+          <t>Nhận "Đạn Nhiệt Áp" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Nhận "Thermobaric Bullets" khi sử dụng Intro Skill hoặc Resonance Skill.</t>
+          <t>Nhận "Đạn Nhiệt Áp" khi sử dụng Kỹ Năng Khởi Động hoặc Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Nhận "Thermobaric Bullets" khi sử dụng Intro Skill hoặc Resonance Skill.</t>
+          <t>Nhận "Đạn Nhiệt Áp" khi sử dụng Kỹ Năng Khởi Động hoặc Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Mỗi khi Danjin gây Havoc DMG bằng Resonance Skill, cô ấy sẽ nhận được "Ruby Blossom".</t>
+          <t>Mỗi lần gây Sát Thương Havoc bằng Resonance Skill, Danjin sẽ nhận được "Hoa Hồng Đỏ".</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Mỗi khi Danjin gây Havoc DMG bằng Resonance Skill, cô ấy sẽ nhận được "Ruby Blossom".</t>
+          <t>Mỗi lần gây Sát Thương Havoc bằng Resonance Skill, Danjin sẽ nhận được "Hoa Hồng Đỏ".</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Nhận hiệu ứng "Annoyance" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Phiền Não" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Nhận hiệu ứng "Annoyance" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Phiền Não" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Nhận "Annoyance" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Phiền Não" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Nhận "Annoyance" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Phiền Não" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Nhận "Quyết Tâm" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Quyết Tâm" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Nhận "Quyết Tâm" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Quyết Tâm" khi Đòn Normal Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>"Resolve" sẽ giảm dần nếu Jiyan không đánh trúng mục tiêu trong vòng 15 giây.</t>
+          <t>"Chỉ số \"Kiên Định\" sẽ giảm dần nếu Jiyan không tấn công mục tiêu trong vòng 15 giây."</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>"Resolve" sẽ giảm dần nếu Jiyan không đánh trúng mục tiêu trong vòng 15 giây.</t>
+          <t>"Chỉ số \"Kiên Định\" sẽ giảm dần nếu Jiyan không tấn công mục tiêu trong vòng 15 giây."</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Khi Basic Attack hoặc Mid-air Attack trúng mục tiêu xuyên qua [Sương Mù], phục hồi 1 [Giọt Sương].</t>
+          <t>Khi Đòn Basic Attack hoặc Đòn Tấn Công Giữa Không trung trúng mục tiêu xuyên qua [Mist], hồi phục 1 [Mist Drop].</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Khi Basic Attack hoặc Mid-air Attack trúng mục tiêu xuyên qua [Sương Mù], phục hồi 1 [Giọt Sương].</t>
+          <t>Khi Đòn Basic Attack hoặc Đòn Tấn Công Giữa Không trung trúng mục tiêu xuyên qua [Mist], hồi phục 1 [Mist Drop].</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Basic Attack IV sẽ tiêu hao toàn bộ &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; để cung cấp lượng "Resolving Caliber" tương đương.</t>
+          <t>Basic Attack IV sẽ tiêu hao toàn bộ &lt;color=#8c7e51&gt;Khiên Đá Vững Chắc&lt;/color&gt; để cung cấp lượng "Năng Lượng Quyết Tâm" tương đương.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Basic Attack IV sẽ tiêu hao toàn bộ &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; để cung cấp lượng "Resolving Caliber" tương đương.</t>
+          <t>Basic Attack IV sẽ tiêu hao toàn bộ &lt;color=#8c7e51&gt;Khiên Đá Vững Chắc&lt;/color&gt; để cung cấp lượng "Năng Lượng Quyết Tâm" tương đương.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Khi bị tấn công, 1 &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; sẽ bị tiêu hao để nhận 1 "Resolving Caliber".</t>
+          <t>Khi bị tấn công, 1 &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; sẽ bị tiêu hao để cấp 1 "Resolving Caliber".</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Khi bị tấn công, 1 &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; sẽ bị tiêu hao để nhận 1 "Resolving Caliber".</t>
+          <t>Khi bị tấn công, 1 &lt;color=#8c7e51&gt;Rocksteady Shield&lt;/color&gt; sẽ bị tiêu hao để cấp 1 "Resolving Caliber".</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nhận 1 "Ý Sát" khi "Tiếng Hú" trúng mục tiêu.</t>
+          <t>Nhận 1 "Sát Khí" khi "Tiếng Hú Sói" trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Nhận 1 "Ý Sát" khi "Tiếng Hú" trúng mục tiêu.</t>
+          <t>Nhận 1 "Sát Khí" khi "Tiếng Hú Sói" trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nhận "Points Phán Xét" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nhận "Points Phán Xét" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Nhận "Judgment Points" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nhận "Judgment Points" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Nhận "Judgment Points" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Nhận "Judgment Points" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Nhận "Points Phán Xét" khi Resonance Liberation trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Liberation trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Nhận "Points Phán Xét" khi Resonance Liberation trúng mục tiêu.</t>
+          <t>Nhận "Điểm Phán Xét" khi Resonance Liberation trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Yuanwu nhận [Sẵn Sàng] mỗi giây khi Resonance Skill &lt;color=#8c7e51&gt;Thunder Wedge&lt;/color&gt; đang tồn tại.</t>
+          <t>Yuanwu nhận [Sẵn Sàng] mỗi giây khi Resonance Skill &lt;color=#8c7e51&gt;Thunder Wedge&lt;/color&gt; tồn tại.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Yuanwu nhận [Sẵn Sàng] mỗi giây khi Resonance Skill &lt;color=#8c7e51&gt;Thunder Wedge&lt;/color&gt; đang tồn tại.</t>
+          <t>Yuanwu nhận [Sẵn Sàng] mỗi giây khi Resonance Skill &lt;color=#8c7e51&gt;Thunder Wedge&lt;/color&gt; tồn tại.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Nhận "Sẵn Sàng" khi các đòn Tấn Công Phối Hợp từ Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Sẵn Sàng" khi Đòn Phối Hợp từ Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Nhận "Sẵn Sàng" khi các đòn Tấn Công Phối Hợp từ Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Sẵn Sàng" khi Đòn Phối Hợp từ Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Khí" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Khí" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi sử dụng Resonance Skill.</t>
+          <t>Nhận "Khí" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi sử dụng Resonance Skill.</t>
+          <t>Nhận "Khí" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Khí" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Nhận "Chi" khi Resonance Skill trúng mục tiêu.</t>
+          <t>Nhận "Khí" khi Resonance Skill trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Nhận "Lion's Spirit" khi sử dụng Resonance Skill.</t>
+          <t>Nhận "Linh Hồn Sư Tử" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Nhận "Lion's Spirit" khi sử dụng Resonance Skill.</t>
+          <t>Nhận "Linh Hồn Sư Tử" khi sử dụng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=#8c7e51&gt;Striding Lion&lt;/color&gt; khi sử dụng Resonance Liberation nếu "Lion's Spirit" đã đầy.</t>
+          <t>Kích hoạt trạng thái &lt;color=#8c7e51&gt;Sư Tử Vươn Mình&lt;/color&gt; khi thi triển Giải Cấp Cộng Hưởng nếu "Linh Hồn Sư Tử" đã đầy.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Enter trạng thái &lt;color=#8c7e51&gt;Striding Lion&lt;/color&gt; khi sử dụng Resonance Liberation nếu "Lion's Spirit" đã đầy.</t>
+          <t>Kích hoạt trạng thái &lt;color=#8c7e51&gt;Sư Tử Vươn Mình&lt;/color&gt; khi thi triển Giải Cấp Cộng Hưởng nếu "Linh Hồn Sư Tử" đã đầy.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Attack kẻ địch để nhận &lt;color=#ffd12f&gt;"Umbra"&lt;/color&gt;, và khi "Umbra" đầy, giữ Basic Attack để vào trạng thái &lt;color=#ffd12f&gt;"Dark Surge"&lt;/color&gt;.</t>
+          <t>Tấn Công kẻ địch để nhận &lt;color=#ffd12f&gt;"Umbra"&lt;/color&gt;, khi "Umbra" đầy, giữ Basic Attack để vào trạng thái &lt;color=#ffd12f&gt;"Dark Surge"&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Nhấn {0} để sử dụng &lt;color=#ffd12f&gt;Resonance Liberation&lt;/color&gt;.</t>
+          <t>Nhấn {0} để tung &lt;color=#ffd12f&gt;Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Nhấn Switch để đổi vũ khí</t>
+          <t>Nhấn Chuyển để đổi vũ khí</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>{0} Nhấn Switch để đổi vũ khí</t>
+          <t>Nhấn Switch để đổi vũ khí.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Chạm vào Switch để đổi vũ khí</t>
+          <t>Nhấn Chuyển để đổi vũ khí</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Chọn Resonance Beacon để di chuyển nhanh</t>
+          <t>Chọn Điểm Cộng Hưởng để Dịch chuyển nhanh</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Chọn Resonance Beacon để di chuyển nhanh</t>
+          <t>Chọn Điểm Cộng Hưởng để Dịch chuyển nhanh</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Chọn Resonance Beacon để di chuyển nhanh</t>
+          <t>Chọn Điểm Cộng Hưởng để Dịch chuyển nhanh</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể xem Outro Skill trong mục Resonators</t>
+          <t>{0} Cậu có thể xem Kỹ năng Outro trong menu Resonator</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Bạn có thể xem Outro Skill trong mục Resonators</t>
+          <t>Bạn có thể xem Kỹ Năng Outro trong menu Resonator</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Resonator</t>
+          <t>Xem Kỹ Năng Resonator</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Resonator</t>
+          <t>Xem Kỹ Năng Resonator</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Resonator</t>
+          <t>Xem Kỹ Năng Resonator</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Illusive Specimen&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
+          <t>Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Mẫu Vật Hư Ảo&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>{0} Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Illusive Specimen&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
+          <t>Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Illusive Specimens&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Illusive Specimen&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
+          <t>Tiếp tục thử thách để nhận &lt;color=#8c7e51&gt;Mẫu Vật Hư Ảo&lt;/color&gt;, có thể đổi lấy Astrites và các phần thưởng khác!</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Tiêu hao liên tục "Năng Lượng Vương Miện" trong quá trình biến hình.</t>
+          <t>Liên tục tiêu hao "Năng Lượng Vương Miện" trong quá trình biến hình.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đã mở khóa các Milestones. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
+          <t>Đã mở khóa cột mốc. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Đã mở khóa các Milestones. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
+          <t>Đã mở khóa cột mốc. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Đã mở khóa các Milestones. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
+          <t>Đã mở khóa cột mốc. Hoàn thành nhiệm vụ để trở nên mạnh mẽ hơn!</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Hoàn thành Basic Training để học tất cả các kỹ năng chiến đấu cần thiết</t>
+          <t>Hoàn thành Huấn Luyện Cơ Bản để nắm vững mọi kỹ năng chiến đấu cần thiết</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Hoàn thành Basic Training để học tất cả các kỹ năng chiến đấu cần thiết</t>
+          <t>Hoàn thành Huấn Luyện Cơ Bản để nắm vững mọi kỹ năng chiến đấu cần thiết</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Hoàn thành Basic Training để học tất cả các kỹ năng chiến đấu cần thiết</t>
+          <t>Hoàn thành Huấn Luyện Cơ Bản để nắm vững mọi kỹ năng chiến đấu cần thiết</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Chọn Yangyang</t>
+          <t>Chọn Dương Dương</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Chọn Yangyang</t>
+          <t>Chọn Dương Dương</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Chọn Yangyang</t>
+          <t>Chọn Dương Dương</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>{0} Trong &lt;color=#8c7e51&gt;Cẩm nang&lt;/color&gt;, bạn có thể xem &lt;color=#8c7e51&gt;Quests Được đề xuất&lt;/color&gt; phù hợp với cấp độ hiện tại.</t>
+          <t>Trong &lt;color=#8c7e51&gt;Cẩm Nang&lt;/color&gt;, bạn có thể xem &lt;color=#8c7e51&gt;Nhiệm Vụ Đề Xuất&lt;/color&gt; phù hợp với cấp độ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Nhận "Umbra" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Umbra" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Nhận "Umbra" khi Basic Attack trúng mục tiêu.</t>
+          <t>Nhận "Umbra" khi Đòn Basic Attack trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Nhận "Umbra" khi Heavy Attack trúng mục tiêu.</t>
+          <t>Nhận "Umbra" khi Đòn Tấn Công Mạnh trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Nhận "Umbra" khi Heavy Attack trúng mục tiêu.</t>
+          <t>Nhận "Umbra" khi Đòn Tấn Công Mạnh trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để vào trạng thái &lt;color=#8c7e51&gt;Dark Surge&lt;/color&gt;.</t>
+          <t>Giữ Basic Attack để bước vào trạng thái &lt;color=#8c7e51&gt;Sóng Âm U Minh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để vào trạng thái &lt;color=#8c7e51&gt;Dark Surge&lt;/color&gt;.</t>
+          <t>Giữ Basic Attack để bước vào trạng thái &lt;color=#8c7e51&gt;Sóng Âm U Minh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=#8c7e51&gt;Dòng Tối&lt;/color&gt;, Basic Attack được tăng cường</t>
+          <t>Trong trạng thái &lt;color=#8c7e51&gt;Dòng Chảy Hắc Ám&lt;/color&gt;, các đòn Basic Attack được tăng cường</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=#8c7e51&gt;Dòng Tối&lt;/color&gt;, Basic Attack được tăng cường</t>
+          <t>Trong trạng thái &lt;color=#8c7e51&gt;Dòng Chảy Hắc Ám&lt;/color&gt;, các đòn Basic Attack được tăng cường</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>"Umbra" sẽ bị tiêu hao liên tục trong trạng thái &lt;color=#8c7e51&gt;Dark Surge&lt;/color&gt;.</t>
+          <t>"Umbra" sẽ liên tục bị tiêu hao khi ở trạng thái &lt;color=#8c7e51&gt;Bùng Nổ Bóng Tối&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>"Umbra" sẽ bị tiêu hao liên tục trong trạng thái &lt;color=#8c7e51&gt;Dark Surge&lt;/color&gt;.</t>
+          <t>"Umbra" sẽ liên tục bị tiêu hao khi ở trạng thái &lt;color=#8c7e51&gt;Bùng Nổ Bóng Tối&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=#8c7e51&gt;Dark Surge&lt;/color&gt;, dùng {0} sau Heavy Attack để thực hiện Chain Attack.</t>
+          <t>Khi ở trạng thái &lt;color=#8c7e51&gt;Dòng Chảy Hắc Ám&lt;/color&gt;, sử dụng {0} sau Đòn Heavy Attack để tung ra Đòn Liên Kết.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=#8c7e51&gt;Dòng Chảy Hắc Ám&lt;/color&gt;, dùng Basic Attack sau Heavy Attack để tung Chain Attack.</t>
+          <t>Khi ở trạng thái &lt;color=#8c7e51&gt;Dòng Chảy Hắc Ám&lt;/color&gt;, sử dụng Đòn Basic Attack sau Đòn Heavy Attack để tung ra Đòn Liên Kết.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Sau khi tung đòn Attack Phái Sinh, {0} để tung đòn Basic Attack Nâng Cao.</t>
+          <t>Sau khi sử dụng Đòn Tấn Công Phái Sinh, {0} để tung ra Đòn Basic Attack Được Tăng Cường.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Nhấn Basic Attack sau khi dùng Heavy Attack để thực hiện Enhanced Basic Attack.</t>
+          <t>Nhấn Basic Attack sau khi dùng Kỹ Năng Nặng để thực hiện Basic Attack Đặc Biệt.</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Tấn công bất kỳ kẻ địch nào bằng Mid-air Attack để tích lũy "Umbra".</t>
+          <t>Tấn công kẻ địch giữa không trung để tích lũy "Umbra".</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tấn công bất kỳ kẻ địch nào bằng Mid-air Attack để tích lũy "Umbra".</t>
+          <t>Tấn công kẻ địch giữa không trung để tích lũy "Umbra".</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Nhấn {0} để mở &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;</t>
+          <t>Nhấn {0} để mở &lt;color=#8c7e51&gt;Hội Ngộ&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>{0} đã &lt;color=#8c7e51&gt;mở khóa Hội Ngộ&lt;/color&gt;</t>
+          <t>{0} &lt;color=#8c7e51&gt;Triệu Hồi&lt;/color&gt; đã được mở khóa.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;, bạn có thể có được những người đồng hành đáng tin cậy và vũ khí tiện dụng</t>
+          <t>Thông qua &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt;, cậu có thể có được những đồng đội đáng tin cậy và vũ khí tiện dụng.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Nhấn {0} để &lt;color=#8c7e51&gt;Switch đổi&lt;/color&gt;</t>
+          <t>Nhấn {0} để &lt;color=#8c7e51&gt;Chuyển&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Khi có 30 Resolve, {0} sử dụng Resonance Liberation để gây thêm DMG.</t>
+          <t>Khi có 30 Điểm Quyết Tâm, {0} dùng Resonance Liberation để gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Khi có 30 Resolve, hãy dùng Resonance Liberation để gây thêm DMG.</t>
+          <t>Khi có 30 Điểm Quyết Tâm, hãy dùng Resonance Liberation để gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Thực hiện Heavy Attack trong khu vực "Frostbite".</t>
+          <t>Thả Đòn Tấn Công Mạnh trong khu vực "Sương Giá".</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Thực hiện Heavy Attack trong khu vực "Frostbite".</t>
+          <t>Thả Đòn Tấn Công Mạnh trong khu vực "Sương Giá".</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Tiêu hao "Năng lượng Quang hợp" để hồi phục tất cả nhân vật trong đội gần đó.</t>
+          <t>Tiêu hao "Năng Lượng Quang Hợp" để hồi phục tất cả Cộng Hưởng Giả trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Tiêu hao "Năng lượng Quang hợp" để hồi phục tất cả nhân vật trong đội gần đó.</t>
+          <t>Tiêu hao "Năng Lượng Quang Hợp" để hồi phục tất cả Cộng Hưởng Giả trong đội gần đó.</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>{0} Increase Cấp Độ Resonator để vượt qua thử thách sắp tới</t>
+          <t>Nâng cấp Cấp Độ Resonator cho {0} để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đến để tăng Cấp Độ Resonator</t>
+          <t>Tăng Cấp Resonator thôi</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tìm kiếm nhiều loại kẻ địch mạnh ở thế giới mở</t>
+          <t>Tìm kiếm nhiều loại kẻ địch mạnh ngoài thế giới mở</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tìm kiếm nhiều loại kẻ địch mạnh ở thế giới mở</t>
+          <t>Tìm kiếm nhiều loại kẻ địch mạnh ngoài thế giới mở</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Tìm kiếm nhiều loại kẻ địch mạnh ở thế giới mở</t>
+          <t>Tìm kiếm nhiều loại kẻ địch mạnh ngoài thế giới mở</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>{0} Increase &lt;color=#8c7e51&gt;Resonator Level&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
+          <t>Tăng &lt;color=#8c7e51&gt;Cấp Độ Resonator&lt;/color&gt; để vượt qua những thử thách sắp tới.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Đến để tăng Cấp Độ Resonator</t>
+          <t>Tăng Cấp Resonator thôi</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>{0}Increase &lt;color=#8c7e51&gt;Cấp Vũ Khí&lt;/color&gt; để vượt qua thử thách sắp tới</t>
+          <t>Nâng cấp &lt;color=#8c7e51&gt;Cấp Vũ Khí&lt;/color&gt; cho {0} để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Đến để tăng Cấp Vũ Khí</t>
+          <t>Tăng Cấp Vũ Khí thôi</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Switch hoặc nâng cấp vũ khí để cải thiện khả năng của Resonators</t>
+          <t>Thay đổi hoặc nâng cấp vũ khí để tăng cường sức mạnh cho Resonator</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>{0} Nâng cấp hoặc Hợp Tấu vũ khí để có chỉ số tốt hơn</t>
+          <t>{0} Nâng cấp hoặc Đồng Điệu vũ khí để tăng chỉ số</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>{0} Equip hoặc nâng cấp &lt;color=#8c7e51&gt;Echoes&lt;/color&gt; để vượt qua thử thách sắp tới</t>
+          <t>{0} Trang bị hoặc nâng cấp &lt;color=#8c7e51&gt;Echo&lt;/color&gt; để vượt qua những thử thách sắp tới</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Đến trang bị hoặc nâng cấp Echoes</t>
+          <t>Đến trang bị hoặc nâng cấp Echo</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Echoes cung cấp cho Resonator chỉ số bổ sung và hiệu ứng Sonata.</t>
+          <t>Echo cung cấp cho Resonator thêm chỉ số và hiệu ứng Sonata.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Bạn có thể trang bị tối đa 5 Echoes. Mỗi Echoes sẽ tăng Chỉ số cho Resonators.</t>
+          <t>Bạn có thể trang bị tối đa 5 Echo. Mỗi Echo sẽ tăng chỉ số cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>{0} Tự Động Equip để xem Echoes đề xuất và trang bị nhanh chóng.</t>
+          <t>Tự Động Trang Bị để xem Echo đề xuất và trang bị nhanh chóng.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>{0} Điều chỉnh góc máy và tư thế nhân vật.</t>
+          <t>Điều chỉnh góc máy và tư thế của {0}.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>{0} Trong &lt;color=#8c7e51&gt;Cẩm nang&lt;/color&gt;, bạn có thể xem &lt;color=#8c7e51&gt;Quests Được đề xuất&lt;/color&gt; phù hợp với cấp độ hiện tại.</t>
+          <t>Trong &lt;color=#8c7e51&gt;Cẩm Nang&lt;/color&gt;, bạn có thể xem &lt;color=#8c7e51&gt;Nhiệm Vụ Đề Xuất&lt;/color&gt; phù hợp với cấp độ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Mở Sổ tay để xem Details Nhiệm vụ</t>
+          <t>Mở Sổ Hướng Dẫn để xem Chi Tiết Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Equip để mở khóa Echo Skill và Bonus Chỉ Số</t>
+          <t>Trang bị để mở khóa Kỹ Năng Echo và Thưởng Tăng Chỉ Số.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Nhấn để chuyển đến thời gian chỉ định</t>
+          <t>Nhấn để chuyển đến thời gian đã chọn</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Thay đổi {0} sang thời gian chỉ định</t>
+          <t>Thay đổi {0} sang thời gian đã chỉ định</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Chạm để đổi sang thời gian đã chỉ định</t>
+          <t>Chạm để chuyển đến thời gian đã chọn</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Dùng Resonance Skill để nhận "Umbra".</t>
+          <t>Kích hoạt Resonance Skill để nhận "Umbra"</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>{0} Tự Động Chọn để nhanh chóng chọn vật liệu cần thiết</t>
+          <t>Tự Động Chọn để nhanh chóng lựa chọn vật liệu cần thiết.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tiếp tục thử thách để trải nghiệm các "Echoes Ảo" khác nhau và nhận thêm phần thưởng!</t>
+          <t>Hãy tiếp tục thử thách với những "Ảo Ảnh Tiếng Vọng" khác nhau để nhận thêm phần thưởng!</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nhấn và giữ để thực hiện &lt;color=#8c7e51&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Nhấn và giữ để tung &lt;color=#8c7e51&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Sử dụng Data Merge để chuyển đổi Echoes không mong muốn thành Echoes mới</t>
+          <t>Sử dụng Data Merge để chuyển đổi Echo không mong muốn thành Echo mới</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Equip tối đa 5 Echoes. Nâng cấp Echoes để tăng chỉ số cho Resonators.</t>
+          <t>Trang bị tối đa 5 Echo. Nâng cấp Echo để tăng chỉ số cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Equip tối đa 5 Echoes. Nâng cấp Echoes để tăng chỉ số cho Resonators.</t>
+          <t>Trang bị tối đa 5 Echo. Nâng cấp Echo để tăng chỉ số cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>{0} Nhận được Echo mới. Equip để tăng Chỉ số Resonator.</t>
+          <t>Nhận được Echo mới. Hãy trang bị để tăng chỉ số Resonator.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Có Echo mới có thể trang bị.</t>
+          <t>Có Echo Mới để trang bị.</t>
         </is>
       </c>
     </row>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nhận được Echo mới. Equip để tăng chỉ số Resonator.</t>
+          <t>Nhận được Echo Mới. Trang bị để tăng chỉ số Resonator.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Có Echo mới có thể trang bị.</t>
+          <t>Có Echo Mới để trang bị.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Attack để ngăn chặn đạn của kẻ địch!</t>
+          <t>Tấn công để đánh bật đạn địch!</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Bật Tự Động Equip để xem Echoes đề xuất và trang bị nhanh.</t>
+          <t>Sử dụng Trang bị tự động để xem Echo đề xuất và trang bị nhanh chóng.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Bật Tự Động Equip để xem Echoes đề xuất và trang bị nhanh.</t>
+          <t>Sử dụng Trang bị tự động để xem Echo đề xuất và trang bị nhanh chóng.</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Events đã mở khóa. Giữ {0} để hiện con trỏ và nhấp để xem menu Events</t>
+          <t>Đã mở khóa sự kiện. Giữ {0} để hiện con trỏ và nhấn để xem menu Sự kiện</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đã mở khóa sự kiện. Chạm để xem Menu Events</t>
+          <t>Đã mở khóa sự kiện. Chạm để xem menu Sự kiện</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Mở {0} Túi Đồ để xem vật phẩm đã nhận.</t>
+          <t>Mở Túi Đồ để xem vật phẩm đã nhận.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Mở Túi Đồ để xem vật phẩm đã nhận</t>
+          <t>Mở Túi Đồ để xem vật phẩm nhận được</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Kiểm tra giới hạn COST hiện tại trong Data Bank</t>
+          <t>Kiểm tra giới hạn COST hiện tại trong Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Kiểm tra giới hạn COST hiện tại trong Data Bank</t>
+          <t>Kiểm tra giới hạn COST hiện tại trong Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Kiểm tra giới hạn COST hiện tại trong Data Bank</t>
+          <t>Kiểm tra giới hạn COST hiện tại trong Ngân Hàng Dữ Liệu</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nâng cấp Kho Dữ liệu để tăng giới hạn COST</t>
+          <t>Nâng cấp Ngân Hàng Dữ Liệu để tăng giới hạn COST</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nâng cấp Kho Dữ liệu để tăng giới hạn COST</t>
+          <t>Nâng cấp Ngân Hàng Dữ Liệu để tăng giới hạn COST</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Nâng cấp Kho Dữ liệu để tăng giới hạn COST</t>
+          <t>Nâng cấp Ngân Hàng Dữ Liệu để tăng giới hạn COST</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>{0} Nhận vũ khí mới. Equip để tăng Stats Resonator</t>
+          <t>Đã nhận vũ khí mới {0}. Trang bị để tăng Chỉ Số Resonator.</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Đã nhận vũ khí mới. Equip để tăng chỉ số Resonator</t>
+          <t>Đã nhận vũ khí mới. Trang bị để tăng chỉ số Resonator.</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Equip vũ khí mới cho Yangyang</t>
+          <t>Trang bị vũ khí mới cho Yangyang</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Equip vũ khí mới cho Yangyang</t>
+          <t>Trang bị vũ khí mới cho Yangyang</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Equip vũ khí mới cho Yangyang</t>
+          <t>Trang bị vũ khí mới cho Yangyang</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Chọn vũ khí cho Resonator tại đây</t>
+          <t>Đổi vũ khí cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Chọn vũ khí cho Resonator tại đây</t>
+          <t>Đổi vũ khí cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Chọn vũ khí cho Resonator tại đây</t>
+          <t>Đổi vũ khí cho Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>{0} Equip Projector để hiển thị Echoes đã hấp thụ.</t>
+          <t>{0} Trang bị Máy Chiếu để hiển thị Echo đã hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>{0} Equip Projector để hiển thị Echoes đã hấp thụ.</t>
+          <t>{0} Trang bị Máy Chiếu để hiển thị Echo đã hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Equip Máy chiếu để hiển thị Echoes đã hấp thụ.</t>
+          <t>Gắn Bộ Chiếu để hiển thị Echo đã hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Có thể trang bị Projector trong Công cụ</t>
+          <t>Bộ chiếu có thể trang bị trong mục Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Có thể trang bị Projector trong Công cụ</t>
+          <t>Bộ chiếu có thể trang bị trong mục Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Có thể trang bị Projector trong Công cụ</t>
+          <t>Bộ chiếu có thể trang bị trong mục Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Công cụ</t>
+          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Công cụ</t>
+          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Công cụ</t>
+          <t>Chọn để trang bị Projector và tạo phím tắt trên vòng Tiện Ích</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Nhấn {0} để mở Map</t>
+          <t>Nhấn {0} để mở Bản Đồ</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Chạm để mở Map</t>
+          <t>Chạm để mở Bản đồ</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>{0}+{1} để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn {0}+{1} để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Nhấn để xem Special Mechanism của Tacet Field này</t>
+          <t>Nhấn để xem Cơ Chế Đặc Biệt của Tổ Tacet này</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Chạm để vào Memetic Tuning</t>
+          <t>Chạm để vào Điều Chỉnh Ngữ Nghĩa</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Chạm để vào Memetic Tuning</t>
+          <t>Chạm để vào Điều Chỉnh Ngữ Nghĩa</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Chạm để vào Memetic Tuning</t>
+          <t>Chạm để vào Điều Chỉnh Ngữ Nghĩa</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Có thể chọn nhiều tổ hợp Memetic Tuning.</t>
+          <t>Có thể chọn nhiều tổ hợp Điều Tần Ngữ Nghĩa.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Có thể chọn nhiều tổ hợp Memetic Tuning.</t>
+          <t>Có thể chọn nhiều tổ hợp Điều Tần Ngữ Nghĩa.</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Có thể chọn nhiều tổ hợp Memetic Tuning.</t>
+          <t>Có thể chọn nhiều tổ hợp Điều Tần Ngữ Nghĩa.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Tỉ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Memetic Tuning đã chọn.</t>
+          <t>Tỷ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Điều Tiết Mô Thức đã chọn.</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Tỉ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Memetic Tuning đã chọn.</t>
+          <t>Tỷ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Điều Tiết Mô Thức đã chọn.</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Tỉ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Memetic Tuning đã chọn.</t>
+          <t>Tỷ lệ phần thưởng sẽ thay đổi tùy theo tổ hợp Điều Tiết Mô Thức đã chọn.</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tokens mang lại hiệu ứng tăng cường mạnh mẽ và có liên hệ mật thiết với quá khứ của Resonators.</t>
+          <t>Mãnh mang lại hiệu ứng tăng cường mạnh mẽ và gắn liền với quá khứ của các Resonator.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tokens mang lại hiệu ứng tăng cường mạnh mẽ và có liên hệ mật thiết với quá khứ của Resonators.</t>
+          <t>Mãnh mang lại hiệu ứng tăng cường mạnh mẽ và gắn liền với quá khứ của các Resonator.</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Tokens mang lại hiệu ứng tăng cường mạnh mẽ và có liên hệ mật thiết với quá khứ của Resonators.</t>
+          <t>Mãnh mang lại hiệu ứng tăng cường mạnh mẽ và gắn liền với quá khứ của các Resonator.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Chọn giai đoạn bạn muốn thử thách.</t>
+          <t>Chọn màn muốn thử thách.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chọn giai đoạn bạn muốn thử thách.</t>
+          <t>Chọn màn muốn thử thách.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Chọn giai đoạn bạn muốn thử thách.</t>
+          <t>Chọn màn muốn thử thách.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Chạm vào Thiết lập và chọn Resonators muốn triển khai.</t>
+          <t>Nhấn Triển Khai và chọn Resonator muốn đặt vào trận.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Chạm vào Thiết lập và chọn Resonators muốn triển khai.</t>
+          <t>Nhấn Triển Khai và chọn Resonator muốn đặt vào trận.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Chạm vào Thiết lập và chọn Resonators muốn triển khai.</t>
+          <t>Nhấn Triển Khai và chọn Resonator muốn đặt vào trận.</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Unlock thêm giai đoạn để mở khóa thêm hiệu ứng.</t>
+          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Mở khóa thêm giai đoạn để mở thêm hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Unlock thêm giai đoạn để mở khóa thêm hiệu ứng.</t>
+          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Mở khóa thêm giai đoạn để mở thêm hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Unlock thêm giai đoạn để mở khóa thêm hiệu ứng.</t>
+          <t>Bạn có thể xem hiệu ứng tăng cường hiện tại. Mở khóa thêm giai đoạn để mở thêm hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chọn Buffs cho giai đoạn này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Buff cho giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chọn Buffs cho giai đoạn này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Buff cho giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để chọn Buffs cho giai đoạn này.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn Buff cho giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Có thể tiến hành huấn luyện kỹ năng chuyên sâu trong các giai đoạn.</t>
+          <t>Huấn luyện kỹ năng chuyên biệt có thể thực hiện trong các giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Có thể tiến hành huấn luyện kỹ năng chuyên sâu trong các giai đoạn.</t>
+          <t>Huấn luyện kỹ năng chuyên biệt có thể thực hiện trong các giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Có thể tiến hành huấn luyện kỹ năng chuyên sâu trong các giai đoạn.</t>
+          <t>Huấn luyện kỹ năng chuyên biệt có thể thực hiện trong các giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>{0} Khi Jinhsi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;.</t>
+          <t>Khi Jinhsi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Hào Quang Tràn Đầy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Khi Jinhsi sử dụng &lt;color=Highlight&gt;Basic Attack Giai đoạn 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;.</t>
+          <t>Khi Jinhsi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Ánh Sáng Tràn Dâng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>{0} Khi Jinhsi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;.</t>
+          <t>Khi Jinhsi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Cấp 4&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng Resonance Skill: &lt;color=Highlight&gt;Hào Quang Tràn Đầy&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>{0} với Resonance Skill &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;.</t>
+          <t>Với Resonance Skill &lt;color=Highlight&gt;Hào Quang Tràn Đầy&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Với Resonance Skill &lt;color=Highlight&gt;Light Tràn&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và进入 &lt;color=Highlight&gt;Incarnation&lt;/color&gt;.</t>
+          <t>Với Resonance Skill &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{0} với Resonance Skill &lt;color=Highlight&gt;Overflowing Radiance&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Incarnation&lt;/color&gt;.</t>
+          <t>Với Resonance Skill &lt;color=Highlight&gt;Hào Quang Tràn Đầy&lt;/color&gt;, Jinhsi gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>{0} Với Resonance Skill &lt;color=Highlight&gt;Illuminous Epiphany&lt;/color&gt;, Jinhsi gây thêm DMG nhưng tiêu hao Forte Gauge.</t>
+          <t>Với Resonance Skill &lt;color=Highlight&gt;Giác Ngộ Quang Minh&lt;/color&gt;, Jinhsi gây thêm DMG nhưng tiêu hao Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>{0} Với Resonance Skill &lt;color=Highlight&gt;Illuminous Epiphany&lt;/color&gt;, Jinhsi gây thêm DMG nhưng tiêu hao Forte Gauge.</t>
+          <t>Với Resonance Skill &lt;color=Highlight&gt;Giác Ngộ Quang Minh&lt;/color&gt;, Jinhsi gây thêm DMG nhưng tiêu hao Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>{0} Sau khi dùng &lt;color=Highlight&gt;Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Chân Nhãn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>{0} Sau khi dùng &lt;color=Highlight&gt;Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack 4&lt;/color&gt;, Changli bước vào trạng thái &lt;color=Highlight&gt;Chân Nhãn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>{0}Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trên mặt đất, cô sẽ thi triển &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trên mặt đất, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Chinh Phục&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trên mặt đất, cô ấy sẽ thi triển &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli dùng &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; trên mặt đất, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Chinh Phục&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Dung Nham&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>{0}Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; trên mặt đất, cô sẽ thi triển &lt;color=Highlight&gt;True Sight: Conquest&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; trên mặt đất, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Chinh Phục&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>{0} Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung, cô ấy sẽ thi triển &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; giữa không trung, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Tích Lũy&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung, cô sẽ thi triển &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc dùng &lt;color=Highlight&gt;Đòn Cơ Bản&lt;/color&gt; trên không, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Tích Lũy&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Dung Nham&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>{0} Khi ở trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung, cô ấy sẽ thi triển &lt;color=Highlight&gt;True Sight: Charge&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;, nếu Changli &lt;color=Highlight&gt;nhảy&lt;/color&gt; hoặc sử dụng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; giữa không trung, cô sẽ thi triển &lt;color=Highlight&gt;Thị Giác Chân Thực: Tích Lũy&lt;/color&gt;, lao về phía kẻ địch và gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Giữ {0} để nạp &lt;color=#8c7e51&gt;Forte Gauge&lt;/color&gt;. Khi Forte Gauge đầy, thả ra để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Mảnh Cổ vật.</t>
+          <t>Giữ {0} để nạp &lt;color=#8c7e51&gt;Thanh Forte&lt;/color&gt;. Khi Thanh Forte đầy, thả ra để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Mảnh Cổ Vật.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Giữ nút **Normal Attack** để nạp &lt;color=#8c7e51&gt;Forte Gauge&lt;/color&gt;. Khi Forte Gauge đầy, thả nút để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Antique.</t>
+          <t>Giữ nút Normal Attack để nạp &lt;color=#8c7e51&gt;Thanh Forte&lt;/color&gt;. Khi Thanh Forte đầy, thả ra để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Món Đồ Cổ.</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Giữ {0} để nạp &lt;color=#8c7e51&gt;Forte Gauge&lt;/color&gt;. Khi Forte Gauge đầy, thả ra để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Mảnh Cổ vật.</t>
+          <t>Giữ {0} để nạp &lt;color=#8c7e51&gt;Thanh Forte&lt;/color&gt;. Khi Thanh Forte đầy, thả ra để thi triển &lt;color=#8c7e51&gt;Frostfall&lt;/color&gt; và nhận một Mảnh Cổ Vật.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Chuông&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Chú Tế của Chuông. Chuông có thể giảm hiệu quả Vibration Strength của kẻ địch.</t>
+          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Chuông Gió&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Chuông. Chuông có thể làm giảm đáng kể Độ Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Đồ Cổ: Chuông Gió&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Cát Tường của Chuông. Chuông có thể giảm hiệu quả Vibration Strength của kẻ địch.</t>
+          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Chuông Gió&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Chuông. Chuông có thể làm giảm đáng kể Độ Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Chuông&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Chú Tế của Chuông. Chuông có thể giảm hiệu quả Vibration Strength của kẻ địch.</t>
+          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Chuông Gió&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Chuông. Chuông có thể làm giảm đáng kể Độ Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ vật: Như Ý&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Phúc Lộc của Như Ý. Như Ý có Hệ số DMG tương đối cao.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Như Ý&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Như Ý. Như Ý có hệ số DMG tương đối cao.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Như Ý&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Phúc Khí Như Ý. Như Ý có Hệ Số DMG tương đối cao.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Như Ý&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Như Ý. Như Ý có hệ số DMG tương đối cao.</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ vật: Như Ý&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Phúc Lộc của Như Ý. Như Ý có Hệ số DMG tương đối cao.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Như Ý&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Như Ý. Như Ý có hệ số DMG tương đối cao.</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#8c7e51&gt;Đồ Cổ: Đỉnh&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Cát Tường của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Đỉnh&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Đỉnh&lt;/color&gt; tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Điềm Lành của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Đỉnh&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#8c7e51&gt;Đồ Cổ: Đỉnh&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Cát Tường của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Đỉnh&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Đỉnh. Đỉnh có thể phá vỡ thế phòng thủ của kẻ địch hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#8c7e51&gt;Huy Chương: Mask&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Mask's Auspice. Mask có thể kéo kẻ địch theo đường đi của nó.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Mặt Nạ&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Mặt Nạ. Mặt Nạ có thể kéo lê kẻ địch theo quỹ đạo của nó.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Với &lt;color=#8c7e51&gt;Cổ Vật: Mask&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Auspice của Mask. Mask có thể kéo kẻ địch dọc theo đường đi của nó.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Mặt Nạ&lt;/color&gt;, tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Mặt Nạ. Mặt Nạ có thể kéo lê kẻ địch theo quỹ đạo của nó.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#8c7e51&gt;Huy Chương: Mask&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và nhận được Mask's Auspice. Mask có thể kéo kẻ địch theo đường đi của nó.</t>
+          <t>Dùng &lt;color=#8c7e51&gt;Cổ Vật: Mặt Nạ&lt;/color&gt;, {0} tấn công để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và nhận được Thiên Ý của Mặt Nạ. Mặt Nạ có thể kéo lê kẻ địch theo quỹ đạo của nó.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Khi đạt 4 Auspices, giữ {0} để thi triển &lt;color=#8c7e51&gt;Tinh hoa Thi ca&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và phục hồi HP cho tất cả thành viên trong đội gần đó.</t>
+          <t>Khi có đủ bốn Dấu Hiệu, giữ {0} để thi triển &lt;color=#8c7e51&gt;Thơ Thi Ca&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và phục hồi HP cho tất cả Cộng Hưởng Giả gần đó.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Khi đạt 4 Điềm Cát, giữ Normal Attack để thi triển &lt;color=#8c7e51&gt;Thơ Tinh Hoa&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và phục hồi HP cho tất cả thành viên đội gần đó.</t>
+          <t>Khi có đủ 4 Tụ Ân, giữ Normal Attack để thi triển &lt;color=#8c7e51&gt;Thi Ca Bản Thể&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và hồi phục HP cho tất cả Cộng Hưởng Giả ở gần.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Khi đạt 4 Auspices, giữ {0} để thi triển &lt;color=#8c7e51&gt;Tinh hoa Thi ca&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và phục hồi HP cho tất cả thành viên trong đội gần đó.</t>
+          <t>Khi có đủ bốn Dấu Hiệu, giữ {0} để thi triển &lt;color=#8c7e51&gt;Thơ Thi Ca&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và phục hồi HP cho tất cả Cộng Hưởng Giả gần đó.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Button Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Đòn Heavy Attack Liên Hoàn &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
+          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Chuỗi Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Button Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Đòn Heavy Attack Liên Hoàn &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
+          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Chuỗi Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Button Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Đòn Heavy Attack Liên Hoàn &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
+          <t>Khi Thanh Forte đầy, giữ &lt;color=Highlight&gt;Nút Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Thanh Forte và thực hiện Chuỗi Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Illation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Dùng {0} để đổi Resonator và sử dụng Intro Skill trong &lt;color=Highlight&gt;Vùng Hư Không Ngoại Vi&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Vùng Hư Không Nội Tại&lt;/color&gt;.</t>
+          <t>Dùng {0} để đổi Resonator và thi triển Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Ngoại Giới Tinh Linh&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Nội Giới Tinh Linh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Chạm để đổi Resonator và sử dụng Intro Skill trong &lt;color=Highlight&gt;Ngoại Giới Tinh Vực&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Nội Giới Tinh Vực&lt;/color&gt;.</t>
+          <t>Chạm để đổi Resonator và sử dụng Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Vùng Hư Không Ngoại Vi&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Vùng Hư Không Nội Tâm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Dùng {0} để đổi Resonator và sử dụng Intro Skill trong &lt;color=Highlight&gt;Vùng Hư Không Ngoại Vi&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Vùng Hư Không Nội Tại&lt;/color&gt;.</t>
+          <t>Dùng {0} để đổi Resonator và thi triển Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Ngoại Giới Tinh Linh&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Nội Giới Tinh Linh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Dùng {0} để chuyển đổi Resonator và sử dụng Intro Skill trong &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt;.</t>
+          <t>Dùng {0} để đổi Resonator và thi triển Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Nội Giới Tinh Linh&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Siêu Giới Tinh Linh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Chạm để đổi Resonator và thi triển Intro Skill trong &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt;.</t>
+          <t>Chạm để đổi Resonator và sử dụng Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Vùng Hư Không Nội Tâm&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Vùng Hư Không Siêu Nhiên&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Dùng {0} để chuyển đổi Resonator và sử dụng Intro Skill trong &lt;color=Highlight&gt;Inner Stellarealm&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Supernal Stellarealm&lt;/color&gt;.</t>
+          <t>Dùng {0} để đổi Resonator và thi triển Kỹ Năng Khởi Động trong &lt;color=Highlight&gt;Nội Giới Tinh Linh&lt;/color&gt; để tiến hóa thành &lt;color=Highlight&gt;Siêu Giới Tinh Linh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Dùng {0} để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Siêu Thực Tinh Vực&lt;/color&gt; và sử dụng Chain Intro Skill &lt;color=Highlight&gt;Discernment&lt;/color&gt;.</t>
+          <t>Dùng {0} để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Siêu Giới Tinh Linh&lt;/color&gt; và thi triển Kỹ Năng Khởi Động Liên Kết &lt;color=Highlight&gt;Phân Định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Chạm để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Siêu Cõi Tinh Tú&lt;/color&gt; để sử dụng Intro Skill Chuỗi &lt;color=Highlight&gt;Phân Định&lt;/color&gt;.</t>
+          <t>Chạm để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Vùng Hư Không Siêu Nhiên&lt;/color&gt; và sử dụng Chuỗi Kỹ Năng Khởi Động &lt;color=Highlight&gt;Thấu Thị&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Dùng {0} để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Siêu Thực Tinh Vực&lt;/color&gt; và sử dụng Chain Intro Skill &lt;color=Highlight&gt;Discernment&lt;/color&gt;.</t>
+          <t>Dùng {0} để chuyển sang Shorekeeper trong &lt;color=Highlight&gt;Siêu Giới Tinh Linh&lt;/color&gt; và thi triển Kỹ Năng Khởi Động Liên Kết &lt;color=Highlight&gt;Phân Định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>{0} Dùng Grapple để tiếp cận Jué nhanh chóng</t>
+          <t>Dùng Grapple để tiếp cận Jué một cách nhanh chóng.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Dùng Grapple để tiếp cận Jué nhanh chóng</t>
+          <t>Dùng Móc Câu để tiếp cận Jué nhanh chóng</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Chạm để thiết lập Lock Mục Tiêu.</t>
+          <t>Chạm để thiết lập Khóa mục tiêu</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Thiết Lập Lock Mục Tiêu</t>
+          <t>Cấu hình Khóa Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Nhấn {0} để trang bị Echoid đã chọn.</t>
+          <t>Nhấn {0} để trang bị Echoid đã chọn</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch để nhận EXP, nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
+          <t>Tích lũy Kinh Nghiệm qua chiến đấu để nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch để nhận EXP, nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
+          <t>Tích lũy Kinh Nghiệm qua chiến đấu để nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch để nhận EXP, nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
+          <t>Tích lũy Kinh Nghiệm qua chiến đấu để nâng cấp và mở khóa kỹ năng mới cho Echoid.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Nhấn {0} để trang bị.</t>
+          <t>Nhấn {0} để trang bị</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Hãy đánh bại tất cả Tacet Discord trước khi hết đếm ngược để nhận điểm thưởng thêm.</t>
+          <t>Tiêu diệt hết Tacet Discord trước khi đếm ngược kết thúc để nhận điểm thưởng.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Hãy đánh bại tất cả Tacet Discord trước khi hết đếm ngược để nhận điểm thưởng thêm.</t>
+          <t>Tiêu diệt hết Tacet Discord trước khi đếm ngược kết thúc để nhận điểm thưởng.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Hãy đánh bại tất cả Tacet Discord trước khi hết đếm ngược để nhận điểm thưởng thêm.</t>
+          <t>Tiêu diệt hết Tacet Discord trước khi đếm ngược kết thúc để nhận điểm thưởng.</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Bảo vệ thiết bị thí nghiệm không bị phá hủy cho đến khi đánh bại tất cả Tacet Discord!</t>
+          <t>Bảo vệ thiết bị thí nghiệm khỏi bị phá hủy cho đến khi tiêu diệt hết Tacet Discord!</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Bảo vệ thiết bị thí nghiệm không bị phá hủy cho đến khi đánh bại tất cả Tacet Discord!</t>
+          <t>Bảo vệ thiết bị thí nghiệm khỏi bị phá hủy cho đến khi tiêu diệt hết Tacet Discord!</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Bảo vệ thiết bị thí nghiệm không bị phá hủy cho đến khi đánh bại tất cả Tacet Discord!</t>
+          <t>Bảo vệ thiết bị thí nghiệm khỏi bị phá hủy cho đến khi tiêu diệt hết Tacet Discord!</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Chạm để xem Cấp Độ Echoid và Skills.</t>
+          <t>Chạm để xem Cấp Độ Echoid và Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chạm để xem Cấp Độ Echoid và Skills.</t>
+          <t>Chạm để xem Cấp Độ Echoid và Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -31061,7 +31061,7 @@
       <c r="M471" t="inlineStr">
         <is>
           <t>Chạm để vào Chế Độ Hợp Tác.
-Bạn có thể chọn cùng Resonator hoặc Echoid với đồng đội.</t>
+Bạn có thể chọn cùng một Resonator hoặc Echoid với đồng đội trong đội.</t>
         </is>
       </c>
     </row>
@@ -31127,8 +31127,8 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Press {0} to enter Chế độ Hợp tác.
-Bạn có thể chọn cùng Resonator hoặc Echoid với thành viên trong nhóm.</t>
+          <t>Nhấn {0} để vào Chế Độ Hợp Tác.
+Bạn có thể chọn cùng Resonator hoặc Echoid với đồng đội trong đội.</t>
         </is>
       </c>
     </row>
@@ -31195,7 +31195,7 @@
       <c r="M473" t="inlineStr">
         <is>
           <t>Chạm để vào Chế Độ Hợp Tác.
-Bạn có thể chọn cùng Resonator hoặc Echoid với đồng đội.</t>
+Bạn có thể chọn cùng một Resonator hoặc Echoid với đồng đội trong đội.</t>
         </is>
       </c>
     </row>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Dùng {0} để bắn với Hoverdroid: Shooter.</t>
+          <t>Dùng {0} để khai hỏa với Hoverdroid: Shooter.</t>
         </is>
       </c>
     </row>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Sử dụng Hoverdroid: Shooter để bắn.</t>
+          <t>Dùng Hoverdroid: Shooter để khai hỏa.</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Nhấn {0} để xem thông tin bản đồ.</t>
+          <t>Dùng {0} để xem thông tin bản đồ.</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Lều Cây Trăng mang theo ước nguyện của mọi người, hướng dẫn công tác chuẩn bị cho Moon-Chasing Festival.</t>
+          <t>Nhà Moontree mang theo những ước nguyện của mọi người, dẫn dắt công tác chuẩn bị cho Lễ Hội Đuổi Trăng.</t>
         </is>
       </c>
     </row>
@@ -31721,7 +31721,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Lều Cây Trăng mang theo ước nguyện của mọi người, hướng dẫn công tác chuẩn bị cho Moon-Chasing Festival.</t>
+          <t>Nhà Moontree mang theo những ước nguyện của mọi người, dẫn dắt công tác chuẩn bị cho Lễ Hội Đuổi Trăng.</t>
         </is>
       </c>
     </row>
@@ -31786,7 +31786,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Lều Cây Trăng mang theo ước nguyện của mọi người, hướng dẫn công tác chuẩn bị cho Moon-Chasing Festival.</t>
+          <t>Nhà Moontree mang theo những ước nguyện của mọi người, dẫn dắt công tác chuẩn bị cho Lễ Hội Đuổi Trăng.</t>
         </is>
       </c>
     </row>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Khi công tác chuẩn bị tiến triển, Độ Nổi Tiếng sẽ tiếp tục tăng.</t>
+          <t>Khi công tác chuẩn bị tiến triển, Độ Phổ Biến sẽ tiếp tục tăng lên.</t>
         </is>
       </c>
     </row>
@@ -31916,7 +31916,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi công tác chuẩn bị tiến triển, Độ Nổi Tiếng sẽ tiếp tục tăng.</t>
+          <t>Khi công tác chuẩn bị tiến triển, Độ Phổ Biến sẽ tiếp tục tăng lên.</t>
         </is>
       </c>
     </row>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi công tác chuẩn bị tiến triển, Độ Nổi Tiếng sẽ tiếp tục tăng.</t>
+          <t>Khi công tác chuẩn bị tiến triển, Độ Phổ Biến sẽ tiếp tục tăng lên.</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Để có được Popularity, bạn cần xây dựng những gian hàng hấp dẫn.</t>
+          <t>Muốn tăng Độ Nổi Tiếng, ngươi cần xây dựng những gian hàng thật hấp dẫn.</t>
         </is>
       </c>
     </row>
@@ -32111,7 +32111,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>{0} Để có được Độ Nổi Tiếng, bạn cần xây dựng những gian hàng hấp dẫn.</t>
+          <t>{0} Muốn có Độ Nổi Tiếng, cậu phải xây những gian hàng thật hấp dẫn.</t>
         </is>
       </c>
     </row>
@@ -32176,7 +32176,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Để có được Popularity, bạn cần xây dựng những gian hàng hấp dẫn.</t>
+          <t>Muốn tăng Độ Nổi Tiếng, ngươi cần xây dựng những gian hàng thật hấp dẫn.</t>
         </is>
       </c>
     </row>
@@ -32241,7 +32241,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Hãy dùng Quỹ ban đầu để xây dựng gian hàng đầu tiên.</t>
+          <t>Hãy dùng số vốn ban đầu để dựng gian hàng đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -32306,7 +32306,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hãy dùng Quỹ ban đầu để xây dựng gian hàng đầu tiên.</t>
+          <t>Hãy dùng số vốn ban đầu để dựng gian hàng đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -32371,7 +32371,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Hãy dùng Quỹ ban đầu để xây dựng gian hàng đầu tiên.</t>
+          <t>Hãy dùng số vốn ban đầu để dựng gian hàng đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Hãy bắt đầu xây dựng gian hàng nào.</t>
+          <t>Bắt tay vào dựng quầy hàng nào.</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>{0} Hãy bắt đầu xây dựng gian hàng nào.</t>
+          <t>{0} bắt tay vào dựng gian hàng nào.</t>
         </is>
       </c>
     </row>
@@ -32566,7 +32566,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Hãy bắt đầu xây dựng gian hàng nào.</t>
+          <t>Bắt tay vào dựng quầy hàng nào.</t>
         </is>
       </c>
     </row>
@@ -32631,7 +32631,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Bạn cần thêm Funds để xây thêm gian hàng. Hoàn thành Wish trong Lodge Wishes là cách tốt để kiếm Funds.</t>
+          <t>Cậu cần thêm Quỹ để xây thêm gian hàng. Hoàn thành các Điều Ước trong Lodge Wishes là cách tốt để kiếm Quỹ đấy.</t>
         </is>
       </c>
     </row>
@@ -32696,7 +32696,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Bạn cần thêm Funds để xây thêm gian hàng. Hoàn thành Wish trong Lodge Wishes là cách tốt để kiếm Funds.</t>
+          <t>Cậu cần thêm Quỹ để xây thêm gian hàng. Hoàn thành các Điều Ước trong Lodge Wishes là cách tốt để kiếm Quỹ đấy.</t>
         </is>
       </c>
     </row>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bạn cần thêm Funds để xây thêm gian hàng. Hoàn thành Wish trong Lodge Wishes là cách tốt để kiếm Funds.</t>
+          <t>Cậu cần thêm Quỹ để xây thêm gian hàng. Hoàn thành các Điều Ước trong Lodge Wishes là cách tốt để kiếm Quỹ đấy.</t>
         </is>
       </c>
     </row>
@@ -32826,7 +32826,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tại đây, bạn sẽ tìm thấy nhiều Điều Ước của mọi người.</t>
+          <t>Nơi đây, cậu sẽ thấy đủ loại Điều Ước của mọi người.</t>
         </is>
       </c>
     </row>
@@ -32891,7 +32891,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Tại đây, bạn sẽ tìm thấy nhiều Điều Ước của mọi người.</t>
+          <t>Nơi đây, cậu sẽ thấy đủ loại Điều Ước của mọi người.</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Tại đây, bạn sẽ tìm thấy nhiều Điều Ước của mọi người.</t>
+          <t>Nơi đây, cậu sẽ thấy đủ loại Điều Ước của mọi người.</t>
         </is>
       </c>
     </row>
@@ -33021,7 +33021,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Có Companions sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
+          <t>Có Đồng Hành bên cạnh sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
         </is>
       </c>
     </row>
